--- a/BVSimulationFiles/110.xlsx
+++ b/BVSimulationFiles/110.xlsx
@@ -6,11 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet1 Copy" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1 Copy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1 Copy Copy" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -414,75 +414,39 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.001491666666666667</v>
+        <v>0.002983333333333333</v>
       </c>
       <c r="D1" t="n">
-        <v>0.002983333333333333</v>
+        <v>0.005966666666666666</v>
       </c>
       <c r="E1" t="n">
-        <v>0.004475</v>
+        <v>0.00895</v>
       </c>
       <c r="F1" t="n">
-        <v>0.005966666666666666</v>
+        <v>0.01193333333333333</v>
       </c>
       <c r="G1" t="n">
-        <v>0.007458333333333332</v>
+        <v>0.01491666666666666</v>
       </c>
       <c r="H1" t="n">
-        <v>0.00895</v>
+        <v>0.0179</v>
       </c>
       <c r="I1" t="n">
-        <v>0.01044166666666667</v>
+        <v>0.02088333333333333</v>
       </c>
       <c r="J1" t="n">
-        <v>0.01193333333333333</v>
+        <v>0.02386666666666666</v>
       </c>
       <c r="K1" t="n">
-        <v>0.013425</v>
+        <v>0.02685</v>
       </c>
       <c r="L1" t="n">
-        <v>0.01491666666666666</v>
+        <v>0.02983333333333333</v>
       </c>
       <c r="M1" t="n">
-        <v>0.01640833333333333</v>
+        <v>0.03281666666666666</v>
       </c>
       <c r="N1" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="O1" t="n">
-        <v>0.01939166666666666</v>
-      </c>
-      <c r="P1" t="n">
-        <v>0.02088333333333333</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>0.022375</v>
-      </c>
-      <c r="R1" t="n">
-        <v>0.02386666666666666</v>
-      </c>
-      <c r="S1" t="n">
-        <v>0.02535833333333333</v>
-      </c>
-      <c r="T1" t="n">
-        <v>0.02685</v>
-      </c>
-      <c r="U1" t="n">
-        <v>0.02834166666666666</v>
-      </c>
-      <c r="V1" t="n">
-        <v>0.02983333333333333</v>
-      </c>
-      <c r="W1" t="n">
-        <v>0.031325</v>
-      </c>
-      <c r="X1" t="n">
-        <v>0.03281666666666666</v>
-      </c>
-      <c r="Y1" t="n">
-        <v>0.03430833333333333</v>
-      </c>
-      <c r="Z1" t="n">
         <v>0.0358</v>
       </c>
     </row>
